--- a/Data/Building/Corridor.EnergyConsumption.xlsx
+++ b/Data/Building/Corridor.EnergyConsumption.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709256803</v>
+        <v>1711844498</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709265863</v>
+        <v>1711858218</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,11 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +562,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709252088</v>
+        <v>1711866488</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +576,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +595,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709258336</v>
+        <v>1711931918</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +609,11 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +632,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709266742</v>
+        <v>1711932329</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +646,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +665,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709337827</v>
+        <v>1711936218</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +679,11 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +702,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709341143</v>
+        <v>1711945096</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +716,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +735,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709344019</v>
+        <v>1712025046</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +749,11 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +772,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709354316</v>
+        <v>1712035827</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +786,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +805,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709426729</v>
+        <v>1712106035</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +819,11 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +842,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709429593</v>
+        <v>1712109038</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +856,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +875,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709431495</v>
+        <v>1712113601</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +889,11 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +912,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709439650</v>
+        <v>1712123246</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +926,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +945,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709442091</v>
+        <v>1712188113</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +955,15 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
+          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +982,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709518028</v>
+        <v>1712190985</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +996,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +1015,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709528017</v>
+        <v>1712196629</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +1025,15 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
+          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1052,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709599446</v>
+        <v>1712201238</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1066,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1085,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709608040</v>
+        <v>1712206554</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1041,10 +1095,11 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
+          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1118,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709616560</v>
+        <v>1712276089</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1132,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1151,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709617295</v>
+        <v>1712278927</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1165,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1184,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709686474</v>
+        <v>1712282582</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1198,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1217,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709861308</v>
+        <v>1712282809</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1231,11 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1254,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709870232</v>
+        <v>1712287906</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1268,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1287,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709943724</v>
+        <v>1712292726</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1233,10 +1297,11 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
+          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1320,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709946580</v>
+        <v>1712535118</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1334,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1353,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709951267</v>
+        <v>1712545035</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1367,11 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1390,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709959863</v>
+        <v>1712554888</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1404,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1423,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1710031884</v>
+        <v>1712623579</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1437,11 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1460,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1710035355</v>
+        <v>1712624920</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1474,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1493,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1710039449</v>
+        <v>1712630396</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1507,11 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1530,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1710045754</v>
+        <v>1712638510</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1544,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1563,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1710049112</v>
+        <v>1712716939</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1573,15 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
+          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1600,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1710120173</v>
+        <v>1712724678</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1614,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1633,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1710120540</v>
+        <v>1712726202</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1647,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1666,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1710125689</v>
+        <v>1712798432</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1680,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1699,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1710207219</v>
+        <v>1712798873</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1709,15 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
+          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1736,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1710211074</v>
+        <v>1712799873</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1750,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1769,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1710212228</v>
+        <v>1712804966</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1783,11 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1806,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1710220582</v>
+        <v>1712811400</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1820,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1839,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1710220832</v>
+        <v>1712811435</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1853,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1872,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1710463517</v>
+        <v>1712881412</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1886,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1905,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1710470047</v>
+        <v>1712883796</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1919,11 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1942,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1710475943</v>
+        <v>1712885654</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1956,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1975,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1710478360</v>
+        <v>1712896173</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1985,15 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
+          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +2012,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1710548666</v>
+        <v>1712897642</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +2026,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2045,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1710549129</v>
+        <v>1712899008</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +2055,11 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
+          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2078,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1710549754</v>
+        <v>1713140134</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2092,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2111,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1710556788</v>
+        <v>1713141745</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2121,11 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
+          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2144,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710565115</v>
+        <v>1713146901</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2158,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2177,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710565232</v>
+        <v>1713152989</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2065,10 +2187,15 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
+          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2214,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710637282</v>
+        <v>1713154283</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2228,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2247,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710638134</v>
+        <v>1713319840</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2261,11 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2284,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710639266</v>
+        <v>1713326950</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2298,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2317,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710645697</v>
+        <v>1713398708</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2331,11 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2354,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710724034</v>
+        <v>1713399626</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2368,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2387,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710729122</v>
+        <v>1713403737</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2401,11 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2424,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710738307</v>
+        <v>1713406375</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2438,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2457,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710738361</v>
+        <v>1713412121</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2471,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2490,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710809847</v>
+        <v>1713487313</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2504,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2523,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710809932</v>
+        <v>1713488570</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2385,10 +2533,11 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
+          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2556,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710811873</v>
+        <v>1713494496</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2570,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2589,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1711073090</v>
+        <v>1713501328</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2449,10 +2599,11 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
+          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2622,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1711081125</v>
+        <v>1713738390</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2636,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2655,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1711084049</v>
+        <v>1713745695</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2513,10 +2665,15 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
+          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2692,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1711154004</v>
+        <v>1713746482</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2706,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2725,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1711162165</v>
+        <v>1713751054</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2739,11 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2762,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1711170716</v>
+        <v>1713757280</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2776,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2795,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1711242871</v>
+        <v>1713847198</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2641,10 +2805,15 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
+          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2832,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1711246172</v>
+        <v>1713849362</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2846,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2865,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1711248323</v>
+        <v>1713918633</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2879,11 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2902,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1711255663</v>
+        <v>1713919627</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2916,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2935,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1711255856</v>
+        <v>1713923560</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2769,10 +2945,15 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
+          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2972,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1711326236</v>
+        <v>1713932869</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2986,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +3005,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1711328911</v>
+        <v>1714003412</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2833,10 +3015,15 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
+          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +3042,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1711331928</v>
+        <v>1714003529</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +3056,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3075,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1711334641</v>
+        <v>1714009232</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3089,11 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3112,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1711339689</v>
+        <v>1714016949</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3126,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3145,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1711340829</v>
+        <v>1714089882</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2961,10 +3155,15 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Corridor.EnergyConsumption.state: LowEnergy</t>
+          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3182,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1711414224</v>
+        <v>1714090018</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3196,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3215,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1711430274</v>
+        <v>1714095907</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3025,10 +3225,81 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
+          <t>Corridor.EnergyConsumption.state: ExcessivelyHigh</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>EnergyConsumption_Change</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Corridor</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1714102875</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Corridor.EnergyConsumption.state: Standard</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>EnergyConsumption_Change</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Corridor</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1714104154</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
           <t>Corridor.EnergyConsumption.state: LowEnergy</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
